--- a/public/templates/template_import_pop.xlsx
+++ b/public/templates/template_import_pop.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>Provinsi</t>
   </si>
@@ -36,37 +36,10 @@
     <t>Tipe POP</t>
   </si>
   <si>
-    <t>Jambi</t>
-  </si>
-  <si>
-    <t>Kota Jambi</t>
-  </si>
-  <si>
-    <t>POP_1MBN10004</t>
-  </si>
-  <si>
-    <t>POP Jambi Kota</t>
-  </si>
-  <si>
-    <t>Shelter</t>
-  </si>
-  <si>
-    <t>POP-SB</t>
-  </si>
-  <si>
-    <t>Kabupaten Batanghari</t>
-  </si>
-  <si>
-    <t>POP_1MBN10005</t>
-  </si>
-  <si>
-    <t>POP Muara Bulian</t>
-  </si>
-  <si>
-    <t>ODC</t>
-  </si>
-  <si>
-    <t>POP-A</t>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
   </si>
   <si>
     <t>PANDUAN PENGISIAN TEMPLATE IMPORT POP</t>
@@ -118,6 +91,18 @@
   </si>
   <si>
     <t>POP-SB | POP-A | POP-B | POP-D</t>
+  </si>
+  <si>
+    <t>Titik koordinat Latitude (derajat desimal)</t>
+  </si>
+  <si>
+    <t>Angka desimal antara -90 sampai 90 (Contoh: -1.608)</t>
+  </si>
+  <si>
+    <t>Titik koordinat Longitude (derajat desimal)</t>
+  </si>
+  <si>
+    <t>Angka desimal antara -180 sampai 180 (Contoh: 103.614)</t>
   </si>
 </sst>
 </file>
@@ -125,7 +110,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -145,15 +130,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
@@ -163,7 +139,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,18 +154,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -212,33 +182,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +492,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="true" style="0"/>
@@ -547,9 +501,11 @@
     <col min="4" max="4" width="28" customWidth="true" style="0"/>
     <col min="5" max="5" width="20" customWidth="true" style="0"/>
     <col min="6" max="6" width="15" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" customHeight="1" ht="24">
+    <row r="1" spans="1:8" customHeight="1" ht="24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,45 +524,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -621,7 +543,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="true" style="0"/>
@@ -631,22 +553,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" customHeight="1" ht="22">
-      <c r="A1" s="3" t="s">
-        <v>17</v>
+      <c r="A1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>21</v>
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -654,13 +576,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -668,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -682,13 +604,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -696,13 +618,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -710,13 +632,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -724,13 +646,41 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
